--- a/artfynd/A 10595-2025 artfynd.xlsx
+++ b/artfynd/A 10595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123236838</v>
       </c>
       <c r="B2" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10595-2025 artfynd.xlsx
+++ b/artfynd/A 10595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123236838</v>
       </c>
       <c r="B2" t="n">
-        <v>100634</v>
+        <v>100636</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10595-2025 artfynd.xlsx
+++ b/artfynd/A 10595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123236838</v>
       </c>
       <c r="B2" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10595-2025 artfynd.xlsx
+++ b/artfynd/A 10595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123236838</v>
       </c>
       <c r="B2" t="n">
-        <v>100642</v>
+        <v>100645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10595-2025 artfynd.xlsx
+++ b/artfynd/A 10595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123236838</v>
       </c>
       <c r="B2" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10595-2025 artfynd.xlsx
+++ b/artfynd/A 10595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123236838</v>
       </c>
       <c r="B2" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10595-2025 artfynd.xlsx
+++ b/artfynd/A 10595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123236838</v>
       </c>
       <c r="B2" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10595-2025 artfynd.xlsx
+++ b/artfynd/A 10595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123236838</v>
       </c>
       <c r="B2" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
